--- a/bolge_adlari.xlsx
+++ b/bolge_adlari.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tavairports-my.sharepoint.com/personal/tboz_tav_aero/Documents/Masaüstü/SUNUM/tahsilat_takibi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="11_F25DC773A252ABDACC10482B991B70025ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4F1098A-CE8E-4F27-B472-6621E9F88EEE}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="11_F25DC773A252ABDACC10482B991B70025ADE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8728A194-B820-472B-AE18-EA74F48F6A31}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$159</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="178">
   <si>
     <t>Region Name</t>
   </si>
@@ -501,6 +501,78 @@
   </si>
   <si>
     <t>İlişkili</t>
+  </si>
+  <si>
+    <t>SET-GENA ADİ ORTAKLIĞI</t>
+  </si>
+  <si>
+    <t>EMSİAR TURİZM OTELCİLİK GAYRİMENKUL YATIRIM İNŞAAT SANAYİ TİCARET ANONİM ŞİRKETİ</t>
+  </si>
+  <si>
+    <t>UNIFREE DUTY FREE İŞLETMECILIĞI A.Ş.</t>
+  </si>
+  <si>
+    <t>EGİS TÜNEL İŞLETMECİLİĞİ A.Ş.</t>
+  </si>
+  <si>
+    <t>PALMİYE TATİL KÖYÜ İŞLETMELERİ TURİZM TİC.AŞ.</t>
+  </si>
+  <si>
+    <t>SANMAR DENIZCILIK MAKINA VE TIC.A.Ş.</t>
+  </si>
+  <si>
+    <t>BRİNKS GÜVENLİK HİZMETLERİ A.Ş.</t>
+  </si>
+  <si>
+    <t>MAYA GAYRİMENKUL GELİŞTİRME A.Ş.</t>
+  </si>
+  <si>
+    <t>ANIK TUR. SAN. VE TİC. A.Ş.</t>
+  </si>
+  <si>
+    <t>GÖKOVA ÖREN MARİNA TUR.İNŞ.VE TİC.A.Ş.</t>
+  </si>
+  <si>
+    <t>KORİNT İNŞAAT TURİZM TİCARET VE SANAYİ A.Ş.</t>
+  </si>
+  <si>
+    <t>S.S.VİLLA BELDE SİTE İŞLETME KOOPERATİFİ</t>
+  </si>
+  <si>
+    <t>YDA İNŞAAT SAN. VE TİC. A.Ş.</t>
+  </si>
+  <si>
+    <t>HAVANA YAYINCILIK TURİZM VE GIDA PAZ. TİC. A.Ş.</t>
+  </si>
+  <si>
+    <t>ETİLER TURİSTİK TESİSLER İŞL.TİC.A.Ş.</t>
+  </si>
+  <si>
+    <t>İSTANBUL FLORENCE NIGHTINGALE HASTANESİ A.Ş.</t>
+  </si>
+  <si>
+    <t>AIR ANKA HAVAYOLLARI A.Ş.</t>
+  </si>
+  <si>
+    <t>BELGIAN IMMIGRATION OFFICE</t>
+  </si>
+  <si>
+    <t>SOCIETE AIR FRANCE MERKEZİ FRANSA İSTANBUL MERKEZ ŞUBESİ</t>
+  </si>
+  <si>
+    <t>K.L.M. HOLLANDA KRALİYET HAVA YOLLARI A.Ş.</t>
+  </si>
+  <si>
+    <t>ETIHAD AIRWAYS</t>
+  </si>
+  <si>
+    <t>BUNDESAMT FÜR FREMDENWESEN UND ASYL</t>
+  </si>
+  <si>
+    <t>İTALYA BAŞKONSOLOSLUĞU</t>
+  </si>
+  <si>
+    <t>RGM TURKEY GAYRİMENKUL YÖNETİM VE İŞLETME A.Ş.</t>
   </si>
 </sst>
 </file>
@@ -556,7 +628,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -565,26 +637,92 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF979991"/>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF979991"/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF979991"/>
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF979991"/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF979991"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -592,15 +730,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -885,7 +1027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C136"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="42.453125" bestFit="1" customWidth="1"/>
@@ -896,1089 +1038,1281 @@
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="5" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="5" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="5" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" t="s">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B153" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B60" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B63" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B67" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B68" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B70" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B71" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B73" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B74" t="s">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B154" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B75" t="s">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B76" t="s">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B77" t="s">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B78" t="s">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B79" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B80" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B81" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B83" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B84" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B85" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B86" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B87" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B88" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B89" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B90" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B91" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B92" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B93" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A94" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B94" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B95" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A96" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B96" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A97" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B97" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A98" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B98" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A99" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B99" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A100" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B100" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B101" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A102" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B102" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A103" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B103" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A104" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B104" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A105" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B105" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A106" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B106" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A107" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B107" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A108" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B108" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A109" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B109" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A110" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B110" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A111" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B111" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A112" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B112" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A113" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B113" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A114" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B114" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A115" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B115" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A116" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B116" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A117" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B117" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A118" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B118" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A119" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B119" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A120" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B120" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A121" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B121" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A122" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B122" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A123" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B123" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A124" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B124" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A125" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B125" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A126" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B126" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A127" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B127" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A128" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B128" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A129" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B129" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A130" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B130" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A131" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B131" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A132" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B132" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A133" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B133" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A134" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B134" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A135" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B135" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A136" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B136" t="s">
-        <v>145</v>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
